--- a/SHIFT.xlsx
+++ b/SHIFT.xlsx
@@ -1,40 +1,426 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GC\Desktop\BOTShift\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C93BBD-F7D3-486B-8539-BD920C91E46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="375" yWindow="0" windowWidth="20175" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Formato" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="111">
+  <si>
+    <t>rut</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>apellidoPaterno</t>
+  </si>
+  <si>
+    <t>apellidoMaterno</t>
+  </si>
+  <si>
+    <t>sexo</t>
+  </si>
+  <si>
+    <t>cargo</t>
+  </si>
+  <si>
+    <t>desde</t>
+  </si>
+  <si>
+    <t>hasta</t>
+  </si>
+  <si>
+    <t>centroCosto</t>
+  </si>
+  <si>
+    <t>sucursal</t>
+  </si>
+  <si>
+    <t>afp</t>
+  </si>
+  <si>
+    <t>isapre</t>
+  </si>
+  <si>
+    <t>sueldoBase</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>TIENDA</t>
+  </si>
+  <si>
+    <t>21622000-5</t>
+  </si>
+  <si>
+    <t>Emily ayleen</t>
+  </si>
+  <si>
+    <t>Aburto</t>
+  </si>
+  <si>
+    <t>Vergara</t>
+  </si>
+  <si>
+    <t>Femenino</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/Operario de Bodega EST</t>
+  </si>
+  <si>
+    <t>FALABELLA RETAIL</t>
+  </si>
+  <si>
+    <t>FALABELLA LOFT 1</t>
+  </si>
+  <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>Fonasa</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/Grupo Colchagua Empresa de Servicios Transitorios S.A.</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO1</t>
+  </si>
+  <si>
+    <t>22708167-8</t>
+  </si>
+  <si>
+    <t>Matias Ignacio</t>
+  </si>
+  <si>
+    <t>Vizcarra</t>
+  </si>
+  <si>
+    <t>Medina</t>
+  </si>
+  <si>
+    <t>Masculino</t>
+  </si>
+  <si>
+    <t>Uno</t>
+  </si>
+  <si>
+    <t>22421166-k</t>
+  </si>
+  <si>
+    <t>Cristofer Antonio</t>
+  </si>
+  <si>
+    <t>Benavides</t>
+  </si>
+  <si>
+    <t>Gutiérrez</t>
+  </si>
+  <si>
+    <t>21619356-3</t>
+  </si>
+  <si>
+    <t>Antonella Beatriz</t>
+  </si>
+  <si>
+    <t>Morales</t>
+  </si>
+  <si>
+    <t>11847694-8</t>
+  </si>
+  <si>
+    <t>Cristian Ignacio</t>
+  </si>
+  <si>
+    <t>Mora</t>
+  </si>
+  <si>
+    <t>Neumann</t>
+  </si>
+  <si>
+    <t>Habitat</t>
+  </si>
+  <si>
+    <t>22710691-3</t>
+  </si>
+  <si>
+    <t>PABLO IGNACIO</t>
+  </si>
+  <si>
+    <t>ALFARO</t>
+  </si>
+  <si>
+    <t>BAHAMONDE</t>
+  </si>
+  <si>
+    <t>20401344-6</t>
+  </si>
+  <si>
+    <t>Adán Ignacio</t>
+  </si>
+  <si>
+    <t>León</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>FONASA</t>
+  </si>
+  <si>
+    <t>12282741-0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jorge Eduardo </t>
+  </si>
+  <si>
+    <t>Astudillo</t>
+  </si>
+  <si>
+    <t>Suarez</t>
+  </si>
+  <si>
+    <t>Provida</t>
+  </si>
+  <si>
+    <t>21386856-k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dilan tomas </t>
+  </si>
+  <si>
+    <t>Toledo</t>
+  </si>
+  <si>
+    <t>Moran</t>
+  </si>
+  <si>
+    <t>UNO</t>
+  </si>
+  <si>
+    <t>16691173-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pablo alberto </t>
+  </si>
+  <si>
+    <t>Pezoa</t>
+  </si>
+  <si>
+    <t>Osorio</t>
+  </si>
+  <si>
+    <t>Capital</t>
+  </si>
+  <si>
+    <t>19569974-7</t>
+  </si>
+  <si>
+    <t>GENESIS CARLINA</t>
+  </si>
+  <si>
+    <t>CARIMAN</t>
+  </si>
+  <si>
+    <t>MANRIQUEZ</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>20145430-1</t>
+  </si>
+  <si>
+    <t>Franco Alejandro</t>
+  </si>
+  <si>
+    <t>Fernandez</t>
+  </si>
+  <si>
+    <t>Quiroz</t>
+  </si>
+  <si>
+    <t>Planvital</t>
+  </si>
+  <si>
+    <t>21574121-4</t>
+  </si>
+  <si>
+    <t>Constanza Valentina</t>
+  </si>
+  <si>
+    <t>Figueroa</t>
+  </si>
+  <si>
+    <t>Barra</t>
+  </si>
+  <si>
+    <t>17690648-0</t>
+  </si>
+  <si>
+    <t>Manuel Branco</t>
+  </si>
+  <si>
+    <t>Gomez</t>
+  </si>
+  <si>
+    <t>Oyarzun</t>
+  </si>
+  <si>
+    <t>18609830-7</t>
+  </si>
+  <si>
+    <t>Hernán Gustavo</t>
+  </si>
+  <si>
+    <t>Larraguibel</t>
+  </si>
+  <si>
+    <t>Maldonado</t>
+  </si>
+  <si>
+    <t>Administrativo</t>
+  </si>
+  <si>
+    <t>22496203-7</t>
+  </si>
+  <si>
+    <t>Lucas andres</t>
+  </si>
+  <si>
+    <t>Luna</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO2</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO3</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO4</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO5</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO6</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO7</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO8</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO9</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO10</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO11</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO12</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO13</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO14</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO15</t>
+  </si>
+  <si>
+    <t>LOGISTICA FALABELLA/LOF1 ACCESO16</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +428,199 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,92 +908,1144 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="44.85546875" customWidth="1"/>
+    <col min="7" max="8" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="27.7109375" customWidth="1"/>
+    <col min="15" max="15" width="35.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>rut</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>apellidoPaterno</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>apellidoMaterno</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>sexo</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>cargo</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>desde</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>hasta</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>centroCosto</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>sucursal</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>afp</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>isapre</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>sueldoBase</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>TIENDA</t>
-        </is>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46272</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46361</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1">
+        <v>46272</v>
+      </c>
+      <c r="H3" s="1">
+        <v>46361</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1">
+        <v>46272</v>
+      </c>
+      <c r="H4" s="1">
+        <v>46361</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1">
+        <v>46272</v>
+      </c>
+      <c r="H5" s="1">
+        <v>46361</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1">
+        <v>46272</v>
+      </c>
+      <c r="H6" s="1">
+        <v>46361</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1">
+        <v>46272</v>
+      </c>
+      <c r="H7" s="1">
+        <v>46361</v>
+      </c>
+      <c r="I7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="1">
+        <v>46272</v>
+      </c>
+      <c r="H8" s="1">
+        <v>46361</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="3">
+        <v>46272</v>
+      </c>
+      <c r="H9" s="3">
+        <f t="shared" ref="H9:H23" si="0">+G9+89</f>
+        <v>46361</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3">
+        <v>46272</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="3">
+        <v>46272</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="3">
+        <v>46272</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="7">
+        <v>46272</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>25</v>
+      </c>
+      <c r="O13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="3">
+        <v>46272</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>25</v>
+      </c>
+      <c r="O14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="3">
+        <v>46272</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="3">
+        <v>46272</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>25</v>
+      </c>
+      <c r="O16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="7">
+        <v>46272</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>25</v>
+      </c>
+      <c r="O17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="7">
+        <v>46272</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I18" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" t="s">
+        <v>64</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>25</v>
+      </c>
+      <c r="O18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="7">
+        <v>46272</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>25</v>
+      </c>
+      <c r="O19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="3">
+        <v>46272</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>25</v>
+      </c>
+      <c r="O20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="7">
+        <v>46272</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>25</v>
+      </c>
+      <c r="O21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="7">
+        <v>46272</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>25</v>
+      </c>
+      <c r="O22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="7">
+        <v>46272</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="0"/>
+        <v>46361</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" t="s">
+        <v>64</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>25</v>
+      </c>
+      <c r="O23" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A9:A23">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9:A23">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Fecha:" prompt="Ingrese una fecha en formato dd/mm/yyyy" sqref="G9:H23" xr:uid="{29F219E1-95F8-4F66-8B72-D142A6B55610}">
+      <formula1>1</formula1>
+      <formula2>109920</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Selección:" prompt="Seleccione un valor de la lista" sqref="L9:L23" xr:uid="{143D326E-E398-4255-8559-296E860EDAA7}">
+      <formula1>"Banmedica,Consalud,Colmena,Cruz Blanca,Mas Vida,Fonasa,Fundación Banco Estado,San Lorenzo,Fusat,Chuquicamata,Isapre Cruz del Norte,Rio Blanco,VidaTres,Isalud,Nueva Mas Vida,IPS Seguro Social,Esencial,Sin Previsión,JEAFOSALE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Selección:" prompt="Seleccione un valor de la lista" sqref="E9:E23" xr:uid="{F012D8FE-C77D-4635-963B-08AFF67D90B0}">
+      <formula1>"M,F,N"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>